--- a/docs/files/luminor/luminor_1H2026_lt.xlsx
+++ b/docs/files/luminor/luminor_1H2026_lt.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,6 +485,11 @@
           <t>2Q2026</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Šaltiniai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -513,6 +519,11 @@
       </c>
       <c r="H2" s="2" t="n">
         <v>37.4</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>L1 p.5; L2 p.7</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -536,6 +547,11 @@
         <v>214.4</v>
       </c>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>L1 p.16</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -558,6 +574,11 @@
         <v>271.7</v>
       </c>
       <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>L1 p.16</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -580,6 +601,11 @@
         <v>65.5</v>
       </c>
       <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>L1 p.16</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -602,6 +628,11 @@
         <v>7.7</v>
       </c>
       <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>L1 p.16</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -624,6 +655,11 @@
         <v>0.14</v>
       </c>
       <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>L1 p.16</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -646,6 +682,11 @@
         <v>2.7</v>
       </c>
       <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>L1 p.16; L2 p.8</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -668,6 +709,11 @@
         <v>11903.2</v>
       </c>
       <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -690,6 +736,11 @@
         <v>12275.5</v>
       </c>
       <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -712,6 +763,11 @@
         <v>19.6</v>
       </c>
       <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>L1; L2 p.8</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -734,6 +790,11 @@
         <v>23.7</v>
       </c>
       <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>L1; L2 p.8</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -756,6 +817,11 @@
         <v>9.9</v>
       </c>
       <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>L1; L2 p.8</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -778,6 +844,11 @@
         <v>36.34</v>
       </c>
       <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>L1; L2 p.8</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -800,6 +871,11 @@
         <v>187</v>
       </c>
       <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>L1; L2 p.8</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -822,6 +898,11 @@
         <v>142.3</v>
       </c>
       <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>L1; L2 p.8</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -844,6 +925,11 @@
         <v>2.1</v>
       </c>
       <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>L1; L2 p.8</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1226,198 +1312,254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Klausimas</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Būsena</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Įrodymas</t>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Anglies (kasyba ar anglies elektrinės) dalis pajamose mažesnė nei 5 %</t>
+          <t>Exclusionary screening (companies)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company is not involved in excluded sectors: controversial and nuclear weapons, tobacco, gambling and restricted sectors in fossil fuel</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Banko skolinimo iškastiniam kurui apribojimai automatiškai nerasti (luminor.ee tvarumo puslapiai nenuskaitomi).</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Bankas pats šiuose sektoriuose neveikia. Informacijos apie skolinimo šiems sektoriams apribojimus automatiškai nerasta (luminor tvarumo puslapiai nenuskaitomi) – patikrinti 2025 m. metinėje ataskaitoje [L2].</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Nėra naujos naftos ir dujų žvalgybos / netradicinės naftos</t>
+          <t>Exclusionary screening (companies)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company does not have red flag/signal related to controversies based on UN Global Compact, OECD Guidelines for Multinational Enterprises or any other relevant principles/standards</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Žr. aukščiau – reikia rankinės patikros.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026 m. raudonų signalų greitoje paieškoje nerasta (2026-10-22). Rekomenduojama patikrinti pinigų plovimo prevencijos istoriją.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Nėra sąsajų su kontroversiškais ginklais, tabaku ar lošimais</t>
+          <t>Exclusionary screening (companies)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company is not in the list of sanctions (add a screenshot)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nerasta informacijos apie skolinimo apribojimus ginklų, tabako ar lošimų sektoriams.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tikrina analitikas vidinėmis priemonėmis (pridėti ekrano nuotrauką). Pastaba: naujas savininkas – OTP Bank (Vengrija) [L1 p.4].</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Nėra rimtų neišspręstų skandalų (korupcija, žmogaus teisės, aplinka)</t>
+          <t>Exclusionary screening (companies)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, issues were not identified from adverse media checks (add a screenshot)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Didelių 2026 m. skandalų greitoje paieškoje nerasta (2026-10-22). Patikrinti PPTP/AML istoriją.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Automatinė naujienų paieška (30 d.) neigiamų antraščių nerado; daugiausia naujienų apie OTP sandorį. Analitikas patvirtina ir prideda ekrano nuotrauką.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Emisijų mažinimo tikslai (Paryžiaus / SBTi) ir pereinamojo laikotarpio planas</t>
+          <t>ESG integration and positive screening (positive answers imply higher allocation)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company is promoting environmental or social characteristics (activities, ESG policy, good ESG rating, etc)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Finansuojamų emisijų tikslai ir NZBA įsipareigojimas automatiškai nerasti.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Žaliųjų paskolų / obligacijų, ESG reitingo ar ESG politikos duomenų automatiškai nerasta.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Tvarumo ataskaitos (CSRD/ESRS ar GRI), atskleistos 1–3 apimties emisijos</t>
+          <t>ESG integration and positive screening (positive answers imply higher allocation)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the activities of the company or it’s strategy is aligned with the taxonomy and/or Paris agreement targets (e.g. net zero commitment)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Tvarumo informacija turėtų būti 2025 m. metinėje ataskaitoje – patikrinti [L2].</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Finansuojamų emisijų tikslų, nulinės emisijos ar NZBA įsipareigojimo automatiškai nerasta.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Teigiamas indėlis (žaliosios pajamos / investicijos, ES taksonomija, žaliosios obligacijos)</t>
+          <t>ESG integration and positive screening (positive answers imply higher allocation)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company does not have yellow flag/signal related to controversies based on UN Global Compact or any other relevant principles/standards</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Žaliųjų paskolų / obligacijų dalis nerasta.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Geltonų signalų greitoje paieškoje nerasta; savininko keitimas (OTP) gali pakeisti ESG politikas [L1 p.4].</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Valdysena – nepriklausoma valdyba, antikorupcijos ir pranešėjų politikos</t>
+          <t>ESG integration and positive screening (positive answers imply higher allocation)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company fulfills the expectations from SEB thematic and sector policies</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Savininko keitimas (OTP) gali pakeisti valdymą; reikia peržiūrėti po sandorio.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SEB neturi atskiros finansų sektoriaus politikos – taikomos bendros taisyklės (UNGC, OECD, žmogaus teisės, Paryžiaus tikslai). Banko duomenų jų vertinimui automatiškai rasta per mažai.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Socialiniai aspektai – sauga, darbo ir žmogaus teisių politikos</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Is there a need for pro-active engagement with the company?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Automatiškai netikrinta.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Siūlomi klausimai: finansuojamų emisijų atskleidimas, iškastinio kuro skolinimo politika, ESG politikos po OTP įsigijimo.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Klausimai įsitraukimui su emitentu</t>
+          <t>Indicators</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the indicators of the company support the targets of sustainability and PAI indicators followed by the Fund</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Siūlomi klausimai: finansuojamų emisijų atskleidimas, iškastinio kuro skolinimo politika, ESG politikos po OTP įsigijimo.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>PAI rodiklių (finansuojamos emisijos, valdybos lyčių įvairovė ir kt.) automatiškai nerasta – patikrinti 2025 m. metinėje ataskaitoje [L2].</t>
         </is>
       </c>
     </row>

--- a/docs/files/luminor/luminor_1H2026_lt.xlsx
+++ b/docs/files/luminor/luminor_1H2026_lt.xlsx
@@ -1444,12 +1444,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Žaliųjų paskolų / obligacijų, ESG reitingo ar ESG politikos duomenų automatiškai nerasta.</t>
+          <t>Tvaraus NT ir atsinaujinančios energetikos paskolos 2025 m. – 305,4 mln. EUR (2024 m. – 182,4 mln.), tikslas – 700 mln. EUR iki 2030 m.; žalios ar su tvarumu susietos obligacijos sudaro 7,4 % obligacijų portfelio; Sustainalytics ESG rizikos reitingas 18,4 (maža rizika) [L2 p.19].</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SEB neturi atskiros finansų sektoriaus politikos – taikomos bendros taisyklės (UNGC, OECD, žmogaus teisės, Paryžiaus tikslai). Banko duomenų jų vertinimui automatiškai rasta per mažai.</t>
+          <t>**Taikoma:** SEB neturi bankų sektoriaus politikos, todėl taikoma investicijų politika bei aplinkosaugos ir socialinė / žmogaus teisių politikos [SP1 p.5, p.7]. **Atitinka:** valdymo ar tarptautinių normų pažeidimų nerasta (greita paieška 2026-10-22); finansuojamos emisijos atskleidžiamos pagal PCAF (3 apimtis – 3,2 mln. t CO2e 2025 m.) [L2 p.22]; tikslas – klimato neutralumas iki 2050 m. [L2 p.19]; tvaraus NT ir atsinaujinančios energetikos paskolos 305,4 mln. EUR, tikslas – 700 mln. EUR iki 2030 m. [L2 p.19]; Sustainalytics ESG rizikos reitingas 18,4 (maža rizika) [L2 p.19]; įsipareigojimas gerbti žmogaus teises [L2 p.18]; PPTFP ir sankcijų atitiktis [L2 p.18]; antikorupcijos priemonės ir pranešėjų kanalai (iš santraukos, patikrinti) [L2 p.23, p.28]. **Nerasta:** viešo skolinimo išimčių sąrašo (anglis, nafta ir dujos, ginklai) ir narystės JT Pasauliniame susitarime / UNEP FI PRB; patikrinti Luminor tvarumo politiką ir pereinamojo laikotarpio plano principus.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1693,6 +1693,72 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SP1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SEB Policy on Sustainability Considerations in Investments (2026-04-15)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://sebgroup.com/sustainability/our-sustainability-strategy/policies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SP3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SEB Environmental Policy on Climate, Nature and Water (2026)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/CBAA255D7EC51026C1257C28002FB11A?opendocument</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SP4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SEB Social and Human Rights Policy (2026-04-28)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/B6C87DACA17DDE3CC1258B5C006292E0?opendocument</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/files/luminor/luminor_1H2026_lt.xlsx
+++ b/docs/files/luminor/luminor_1H2026_lt.xlsx
@@ -537,8 +537,12 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+      <c r="C3" s="2" t="n">
+        <v>507.7</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>214.7</v>
+      </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n">
         <v>427.3</v>
@@ -549,7 +553,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16</t>
+          <t>L1 p.16; L1 p.5; L2 p.7</t>
         </is>
       </c>
     </row>
@@ -564,8 +568,12 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
+      <c r="C4" s="2" t="n">
+        <v>632.8</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>269.5</v>
+      </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n">
         <v>544.7</v>
@@ -576,7 +584,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16</t>
+          <t>L1 p.16; L1 p.5; L2 p.7</t>
         </is>
       </c>
     </row>
@@ -591,8 +599,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="C5" s="2" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>60.1</v>
+      </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n">
         <v>64.7</v>
@@ -603,7 +615,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16</t>
+          <t>L1 p.16; L1 p.9; L2 p.2</t>
         </is>
       </c>
     </row>
@@ -618,7 +630,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n">
@@ -630,7 +644,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16</t>
+          <t>L1 p.16; L2 p.2</t>
         </is>
       </c>
     </row>
@@ -672,8 +686,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
+      <c r="C8" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2.84</v>
+      </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n">
         <v>2.71</v>
@@ -684,7 +702,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16; L2 p.8</t>
+          <t>L1 p.16; L1 p.9; L2 p.7; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -699,8 +717,12 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n">
+        <v>10535.4</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>10820.5</v>
+      </c>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n">
         <v>11491.4</v>
@@ -711,7 +733,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1; L1 p.6; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -726,8 +748,12 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n">
+        <v>11352.7</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>11240.5</v>
+      </c>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n">
         <v>11510.7</v>
@@ -738,7 +764,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1; L1 p.6; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -753,8 +779,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>20.6</v>
+      </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n">
         <v>20.2</v>
@@ -765,7 +795,7 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.7; L2 p.8; L2 p.9</t>
         </is>
       </c>
     </row>
@@ -780,8 +810,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>25.2</v>
+      </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n">
         <v>24.6</v>
@@ -792,7 +826,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.7; L2 p.8; L2 p.9</t>
         </is>
       </c>
     </row>
@@ -807,8 +841,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n">
         <v>10</v>
@@ -819,7 +857,7 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.7; L2 p.8; L2 p.9</t>
         </is>
       </c>
     </row>
@@ -861,8 +899,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>163.3</v>
+      </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n">
         <v>174.6</v>
@@ -873,7 +915,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.6; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -888,8 +930,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>133.8</v>
+      </c>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n">
         <v>134.1</v>
@@ -900,7 +946,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.6; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -915,8 +961,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1.7</v>
+      </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n">
         <v>2</v>
@@ -927,7 +977,7 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.8; L2 p.10; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -1038,20 +1088,24 @@
           <t>2027-06-08</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>matured</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Amount/ranking/call date not on issuer placements page - check Final Terms</t>
+          <t>Senior preferred. Called at par on 2026-06-08: Luminor redeemed this EUR 300m senior bond (3M EURIBOR+4.471% after call) in 1H 2026</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://luminor.lv/en/placements</t>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-11.pdf</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1150,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Placements page shows 12.06.2028 in maturity column but 2029 in name - likely call 2028 / final 2029; check Final Terms</t>
+          <t>Senior preferred; callable at par 2028-06-12, then 3M EURIBOR+1.55%</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://luminor.lv/en/placements</t>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-15.pdf</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1188,11 @@
           <t>2028-09-10</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>active</t>
@@ -1142,12 +1200,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Amount/ranking/call date not on issuer placements page - check Final Terms</t>
+          <t>Senior preferred; callable at par 2027-09-10, then 3M EURIBOR+1.50%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://luminor.lv/en/placements</t>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-13.pdf</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1217,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Luminor Bank 7.375% perpetual (AT1?)</t>
+          <t>Luminor 7.375% perpetual</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1184,7 +1242,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Perpetual; annual report mentions inaugural EUR 150m AT1 in 2025 - link to this ISIN not confirmed</t>
+          <t>Perpetual, issued 2025-02-12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1356,12 +1414,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bankas pats šiuose sektoriuose neveikia. Informacijos apie skolinimo šiems sektoriams apribojimus automatiškai nerasta (luminor tvarumo puslapiai nenuskaitomi) – patikrinti 2025 m. metinėje ataskaitoje [L2].</t>
+          <t>Bankas nevykdo veiklos išskirtuose sektoriuose. Tvaraus NT ir atsinaujinančios energetikos paskolos auga (2025 m. – 305,4 mln. EUR) [L2 p.19].</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1436,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026 m. raudonų signalų greitoje paieškoje nerasta (2026-10-22). Rekomenduojama patikrinti pinigų plovimo prevencijos istoriją.</t>
+          <t>Su JT Pasauliniu susitarimu ar OECD gairėmis susijusių ginčų viešuose šaltiniuose ir naujienose nerasta (2026-10-22). Baudų dėl pinigų plovimo prevencijos neskelbta; vienintelė 2025 m. priežiūros pastaba – Finantsinspektsioon nurodymas dėl bazinių mokėjimo paslaugų tvarkos [L2 p.16].</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1463,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tikrina analitikas vidinėmis priemonėmis (pridėti ekrano nuotrauką). Pastaba: naujas savininkas – OTP Bank (Vengrija) [L1 p.4].</t>
+          <t>Automatinė patikra ES, JT, JAV OFAC ir JK konsoliduotuose sankcijų sąrašuose.</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1480,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Automatinė naujienų paieška (30 d.) neigiamų antraščių nerado; daugiausia naujienų apie OTP sandorį. Analitikas patvirtina ir prideda ekrano nuotrauką.</t>
+          <t>Automatinė naujienų paieška (paskutinės 30 d., 2026-10-22) neigiamų naujienų nerado; dauguma naujienų – apie OTP Bank sandorį.</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1524,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Finansuojamų emisijų tikslų, nulinės emisijos ar NZBA įsipareigojimo automatiškai nerasta.</t>
+          <t>Tikslas – klimato neutralumas iki 2050 m. [L2 p.19]; finansuojamos emisijos skaičiuojamos PCAF metodu [L2 p.22]; žalios ar su tvarumu susietos obligacijos sudaro 7,4 % obligacijų portfelio, tikslas – 50 % iki 2030 m. [L2 p.19].</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1546,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Geltonų signalų greitoje paieškoje nerasta; savininko keitimas (OTP) gali pakeisti ESG politikas [L1 p.4].</t>
+          <t>Geltonų signalų nerasta. Gavus leidimus savininku taps OTP Bank (Vengrija) [L1 p.4].</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1573,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>**Taikoma:** SEB neturi bankų sektoriaus politikos, todėl taikoma investicijų politika bei aplinkosaugos ir socialinė / žmogaus teisių politikos [SP1 p.5, p.7]. **Atitinka:** valdymo ar tarptautinių normų pažeidimų nerasta (greita paieška 2026-10-22); finansuojamos emisijos atskleidžiamos pagal PCAF (3 apimtis – 3,2 mln. t CO2e 2025 m.) [L2 p.22]; tikslas – klimato neutralumas iki 2050 m. [L2 p.19]; tvaraus NT ir atsinaujinančios energetikos paskolos 305,4 mln. EUR, tikslas – 700 mln. EUR iki 2030 m. [L2 p.19]; Sustainalytics ESG rizikos reitingas 18,4 (maža rizika) [L2 p.19]; įsipareigojimas gerbti žmogaus teises [L2 p.18]; PPTFP ir sankcijų atitiktis [L2 p.18]; antikorupcijos priemonės ir pranešėjų kanalai (iš santraukos, patikrinti) [L2 p.23, p.28]. **Nerasta:** viešo skolinimo išimčių sąrašo (anglis, nafta ir dujos, ginklai) ir narystės JT Pasauliniame susitarime / UNEP FI PRB; patikrinti Luminor tvarumo politiką ir pereinamojo laikotarpio plano principus.</t>
+          <t>**Taikoma:** SEB neturi bankų sektoriaus politikos, todėl taikoma investicijų politika bei aplinkosaugos ir socialinė / žmogaus teisių politikos [SP1 p.5, p.7]. **Atitinka:** valdymo ar tarptautinių normų pažeidimų nerasta (greita paieška 2026-10-22); finansuojamos emisijos atskleidžiamos pagal PCAF (3 apimtis – 3,2 mln. t CO2e 2025 m.) [L2 p.22]; tikslas – klimato neutralumas iki 2050 m. [L2 p.19]; tvaraus NT ir atsinaujinančios energetikos paskolos 305,4 mln. EUR, tikslas – 700 mln. EUR iki 2030 m. [L2 p.19]; Sustainalytics ESG rizikos reitingas 18,4 (maža rizika) [L2 p.19]; įsipareigojimas gerbti žmogaus teises [L2 p.18]; PPTFP ir sankcijų atitiktis [L2 p.18]; antikorupcijos priemonės ir pranešėjų kanalai [L2 p.23, p.28]. **Galėtų būti geriau:** viešo skolinimo išimčių sąrašo (anglis, nafta ir dujos, ginklai) ir narystės JT Pasauliniame susitarime nerasta.</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1590,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Siūlomi klausimai: finansuojamų emisijų atskleidimas, iškastinio kuro skolinimo politika, ESG politikos po OTP įsigijimo.</t>
+          <t>Nereikia: kapitalas, likvidumas ir ESG praktika – tvirti.</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1612,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>PAI rodiklių (finansuojamos emisijos, valdybos lyčių įvairovė ir kt.) automatiškai nerasta – patikrinti 2025 m. metinėje ataskaitoje [L2].</t>
+          <t>Finansuojamos emisijos (3 apimtis) 2025 m. – 3,2 mln. t CO2e, PCAF metodas [L2 p.22]; moterų dalis stebėtojų taryboje – 33,3 % (tikslas 40 %) [L2 p.29]; Sustainalytics ESG rizikos reitingas 18,4, maža rizika [L2 p.19].</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1759,6 +1817,72 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Final Terms Series 11 - 7.750% notes XS2633112565</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-11.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Final Terms Series 13 - 4.042% notes XS2888497067</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-13.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Final Terms Series 15 - 3.551% notes XS3079969104</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-15.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/files/luminor/luminor_1H2026_lt.xlsx
+++ b/docs/files/luminor/luminor_1H2026_lt.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">

--- a/docs/files/luminor/luminor_1H2026_lt.xlsx
+++ b/docs/files/luminor/luminor_1H2026_lt.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">

--- a/docs/files/luminor/luminor_1H2026_lt.xlsx
+++ b/docs/files/luminor/luminor_1H2026_lt.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">

--- a/docs/files/luminor/luminor_1H2026_lt.xlsx
+++ b/docs/files/luminor/luminor_1H2026_lt.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
